--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1005,34 +1005,34 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>390.9</v>
+        <v>395.44</v>
       </c>
       <c r="U5" t="n">
-        <v>343.99</v>
+        <v>347.99</v>
       </c>
       <c r="V5" t="n">
-        <v>390.9</v>
+        <v>395.44</v>
       </c>
       <c r="W5" t="n">
         <v>12</v>
       </c>
       <c r="X5" t="n">
-        <v>32.57</v>
+        <v>32.95</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1200051163980557</v>
+        <v>0.1199929192797896</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.03453588767115323</v>
+        <v>-0.04563349521537974</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.150396520849322</v>
+        <v>-0.1601507181873356</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6994166410807492</v>
+        <v>0.6798179059180576</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>486.35</v>
+        <v>509.08</v>
       </c>
       <c r="U17" t="n">
-        <v>427.99</v>
+        <v>447.99</v>
       </c>
       <c r="V17" t="n">
-        <v>486.35</v>
+        <v>509.08</v>
       </c>
       <c r="W17" t="n">
         <v>12</v>
       </c>
       <c r="X17" t="n">
-        <v>40.53</v>
+        <v>42.42</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1199958877351701</v>
+        <v>0.1200007857311227</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.01976681698170524</v>
+        <v>-0.06352820375454815</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.137390767965457</v>
+        <v>-0.1759055551190383</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.7251418702195904</v>
+        <v>0.6482791136256483</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Competitivo</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4248,7 +4248,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5070,7 +5070,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6482,7 +6482,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6596,7 +6596,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6710,7 +6710,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7296,7 +7296,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -7528,7 +7528,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7642,7 +7642,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7844,7 +7844,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7932,7 +7932,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8164,7 +8164,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8252,7 +8252,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -8458,7 +8458,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -8546,7 +8546,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -12220,7 +12220,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -13028,7 +13028,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -13167,15 +13167,11 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -13193,44 +13189,20 @@
       <c r="R112" t="n">
         <v>85.95</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Pneu Goodyear Aro 15 EfficientGrip Performance 195/65R15 91H</t>
-        </is>
-      </c>
-      <c r="T112" t="n">
-        <v>588.78</v>
-      </c>
-      <c r="U112" t="n">
-        <v>529.9</v>
-      </c>
-      <c r="V112" t="n">
-        <v>588.78</v>
-      </c>
-      <c r="W112" t="n">
-        <v>10</v>
-      </c>
-      <c r="X112" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0.1000033968545128</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>-0.02681638044914125</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>-0.1241380481673968</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0.4599966026838798</v>
-      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Sem dado</t>
         </is>
       </c>
     </row>
@@ -13260,7 +13232,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -13376,7 +13348,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -13492,7 +13464,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13588,7 +13560,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13704,7 +13676,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13820,7 +13792,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -13936,7 +13908,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -14052,7 +14024,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -14168,7 +14140,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -14284,7 +14256,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -14396,7 +14368,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -14508,7 +14480,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14533,13 +14505,13 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -14562,39 +14534,19 @@
           <t>Pneu Goodyear Aro 14 Assurance Maxlife 185/65R14 86H</t>
         </is>
       </c>
-      <c r="T124" t="n">
-        <v>527.67</v>
-      </c>
-      <c r="U124" t="n">
-        <v>474.9</v>
-      </c>
-      <c r="V124" t="n">
-        <v>527.67</v>
-      </c>
-      <c r="W124" t="n">
-        <v>10</v>
-      </c>
-      <c r="X124" t="n">
-        <v>52.76</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0.100005685371539</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>-0.05032638450200033</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>-0.1452991452991452</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>0.4247536012130402</v>
-      </c>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14572,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -14736,7 +14688,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14852,7 +14804,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14968,7 +14920,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -15064,7 +15016,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -15176,7 +15128,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -15292,7 +15244,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15404,7 +15356,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15496,7 +15448,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15588,7 +15540,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15700,7 +15652,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15792,7 +15744,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15908,7 +15860,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -16020,7 +15972,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -16112,7 +16064,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -16208,7 +16160,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -16320,7 +16272,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -16412,7 +16364,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -16496,7 +16448,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10-22 11:50</t>
+          <t>2026-10-23 08:50</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>424.99</v>
+        <v>418.17</v>
       </c>
       <c r="U10" t="n">
-        <v>373.99</v>
+        <v>367.99</v>
       </c>
       <c r="V10" t="n">
-        <v>424.99</v>
+        <v>418.17</v>
       </c>
       <c r="W10" t="n">
         <v>12</v>
       </c>
       <c r="X10" t="n">
-        <v>35.42</v>
+        <v>34.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1200028235958494</v>
+        <v>0.119999043451228</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1119816037861975</v>
+        <v>-0.09750264952851984</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.2185463187369114</v>
+        <v>-0.205801468302365</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5626764539808018</v>
+        <v>0.588235294117647</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3365,38 +3365,38 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>493.17</v>
+        <v>453.41</v>
       </c>
       <c r="U25" t="n">
-        <v>433.99</v>
+        <v>399</v>
       </c>
       <c r="V25" t="n">
-        <v>493.17</v>
+        <v>453.41</v>
       </c>
       <c r="W25" t="n">
         <v>12</v>
       </c>
       <c r="X25" t="n">
-        <v>41.1</v>
+        <v>37.78</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1199991889206562</v>
+        <v>0.12000176440749</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.06152215488836144</v>
+        <v>0.02077694235588967</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.1741387351217633</v>
+        <v>-0.1017180917932997</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.651581508515815</v>
+        <v>0.7967178401270512</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Na média</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3601,34 +3601,34 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>474.99</v>
+        <v>442.05</v>
       </c>
       <c r="U27" t="n">
-        <v>417.99</v>
+        <v>389</v>
       </c>
       <c r="V27" t="n">
-        <v>474.99</v>
+        <v>442.05</v>
       </c>
       <c r="W27" t="n">
         <v>12</v>
       </c>
       <c r="X27" t="n">
-        <v>39.58</v>
+        <v>36.84</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1200025263689762</v>
+        <v>0.1200090487501414</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.04650828967200171</v>
+        <v>0.02455012853470451</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.1609297037832376</v>
+        <v>-0.09840515778758063</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6781202627589693</v>
+        <v>0.8029315960912051</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4248,7 +4248,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4509,15 +4509,13 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>8</v>
-      </c>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -4535,44 +4533,20 @@
       <c r="R35" t="n">
         <v>87.41</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Pneu 205/60R15 Goodyear Efficientgrip Performance 91H CrossFox Saveiro Cross</t>
-        </is>
-      </c>
-      <c r="T35" t="n">
-        <v>622.72</v>
-      </c>
-      <c r="U35" t="n">
-        <v>547.99</v>
-      </c>
-      <c r="V35" t="n">
-        <v>622.72</v>
-      </c>
-      <c r="W35" t="n">
-        <v>12</v>
-      </c>
-      <c r="X35" t="n">
-        <v>51.89</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.1200057810894142</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>-0.04297523677439363</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-0.1578237410071942</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.6845249566390441</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4576,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4720,7 +4694,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4838,7 +4812,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4956,7 +4930,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5070,7 +5044,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5188,7 +5162,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5306,7 +5280,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5424,7 +5398,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5542,7 +5516,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5660,7 +5634,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5778,7 +5752,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5896,7 +5870,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6014,7 +5988,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6132,7 +6106,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6250,7 +6224,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6368,7 +6342,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6482,7 +6456,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6596,7 +6570,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6710,7 +6684,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6828,7 +6802,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6946,7 +6920,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7064,7 +7038,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7182,7 +7156,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7296,7 +7270,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -7414,7 +7388,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -7528,7 +7502,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7642,7 +7616,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7730,7 +7704,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7844,7 +7818,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7932,7 +7906,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8050,7 +8024,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8164,7 +8138,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8252,7 +8226,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8344,7 +8318,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -8458,7 +8432,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -8546,7 +8520,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8630,7 +8604,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8748,7 +8722,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8809,28 +8783,28 @@
         <v>319.9</v>
       </c>
       <c r="V73" t="n">
-        <v>355.45</v>
+        <v>342.79</v>
       </c>
       <c r="W73" t="n">
         <v>10</v>
       </c>
       <c r="X73" t="n">
-        <v>35.54</v>
+        <v>34.27</v>
       </c>
       <c r="Y73" t="n">
         <v>0.1000140666760445</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>0.03561682374454911</v>
       </c>
       <c r="AA73" t="n">
         <v>-0.09846827133479208</v>
       </c>
       <c r="AB73" t="n">
-        <v>-0.1886341257560838</v>
+        <v>-0.1586685725954667</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.3525604952166572</v>
+        <v>0.4026845637583891</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
@@ -8864,7 +8838,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8925,28 +8899,28 @@
         <v>394.9</v>
       </c>
       <c r="V74" t="n">
-        <v>481.59</v>
+        <v>464.44</v>
       </c>
       <c r="W74" t="n">
         <v>10</v>
       </c>
       <c r="X74" t="n">
-        <v>48.15</v>
+        <v>46.44</v>
       </c>
       <c r="Y74" t="n">
         <v>0.1800078905292885</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>0.0356112045515895</v>
       </c>
       <c r="AA74" t="n">
         <v>0.007039756900481198</v>
       </c>
       <c r="AB74" t="n">
-        <v>-0.1742353454183018</v>
+        <v>-0.1437430023253811</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.3765316718587748</v>
+        <v>0.4272179155900087</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
@@ -8980,7 +8954,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9041,28 +9015,28 @@
         <v>679.9</v>
       </c>
       <c r="V75" t="n">
-        <v>755.45</v>
+        <v>728.55</v>
       </c>
       <c r="W75" t="n">
         <v>10</v>
       </c>
       <c r="X75" t="n">
-        <v>75.54000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="Y75" t="n">
         <v>0.1000066185717123</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>0.03560791581176792</v>
       </c>
       <c r="AA75" t="n">
         <v>-0.1438005589057214</v>
       </c>
       <c r="AB75" t="n">
-        <v>-0.2294261698325502</v>
+        <v>-0.2009745384668176</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.2843526608419378</v>
+        <v>0.3317776252573783</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
@@ -9096,7 +9070,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9157,28 +9131,28 @@
         <v>349.9</v>
       </c>
       <c r="V76" t="n">
-        <v>397.62</v>
+        <v>383.46</v>
       </c>
       <c r="W76" t="n">
         <v>10</v>
       </c>
       <c r="X76" t="n">
-        <v>39.76</v>
+        <v>38.34</v>
       </c>
       <c r="Y76" t="n">
         <v>0.1200140837986018</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>0.03561189074996229</v>
       </c>
       <c r="AA76" t="n">
         <v>-0.0508430980280079</v>
       </c>
       <c r="AB76" t="n">
-        <v>-0.1647552939992958</v>
+        <v>-0.1339122724664893</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.3921026156941652</v>
+        <v>0.4436619718309858</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
@@ -9212,7 +9186,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9237,13 +9211,13 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Oportunidade: só a Roma tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -9266,19 +9240,39 @@
           <t>Pneu Kelly by Goodyear Aro 13 Edge Touring 2 175/70R13 82T</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
+      <c r="T77" t="n">
+        <v>333.23</v>
+      </c>
+      <c r="U77" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="V77" t="n">
+        <v>321.36</v>
+      </c>
+      <c r="W77" t="n">
+        <v>10</v>
+      </c>
+      <c r="X77" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0.1000210065120188</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.03562104252318221</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>-0.06748916305435126</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>-0.1297610156833457</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.4506691565515093</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Concorrente sem estoque</t>
+          <t>Competitivo</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9302,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9369,28 +9363,28 @@
         <v>419.9</v>
       </c>
       <c r="V78" t="n">
-        <v>512.08</v>
+        <v>493.84</v>
       </c>
       <c r="W78" t="n">
         <v>10</v>
       </c>
       <c r="X78" t="n">
-        <v>51.2</v>
+        <v>49.38</v>
       </c>
       <c r="Y78" t="n">
         <v>0.1800109357912827</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>0.03561943446336524</v>
       </c>
       <c r="AA78" t="n">
         <v>-0.03003095975232184</v>
       </c>
       <c r="AB78" t="n">
-        <v>-0.2046359943758788</v>
+        <v>-0.1752591932609752</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.3257812499999999</v>
+        <v>0.3746456055083027</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
@@ -9424,7 +9418,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9520,7 +9514,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9616,7 +9610,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9677,28 +9671,28 @@
         <v>379.89</v>
       </c>
       <c r="V81" t="n">
-        <v>431.7</v>
+        <v>416.33</v>
       </c>
       <c r="W81" t="n">
         <v>10</v>
       </c>
       <c r="X81" t="n">
-        <v>43.17</v>
+        <v>41.63</v>
       </c>
       <c r="Y81" t="n">
         <v>0.1200138985406533</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>0.0356034283066945</v>
       </c>
       <c r="AA81" t="n">
         <v>-0.1257732501513595</v>
       </c>
       <c r="AB81" t="n">
-        <v>-0.2306926106092193</v>
+        <v>-0.2022914514928061</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.2821403752605975</v>
+        <v>0.3295700216190247</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
@@ -9732,7 +9726,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9793,28 +9787,28 @@
         <v>439.9</v>
       </c>
       <c r="V82" t="n">
-        <v>536.47</v>
+        <v>517.37</v>
       </c>
       <c r="W82" t="n">
         <v>10</v>
       </c>
       <c r="X82" t="n">
-        <v>53.64</v>
+        <v>51.73</v>
       </c>
       <c r="Y82" t="n">
         <v>0.1800100658005108</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>0.03560310921393561</v>
       </c>
       <c r="AA82" t="n">
         <v>-0.01052511934530576</v>
       </c>
       <c r="AB82" t="n">
-        <v>-0.1886405577199098</v>
+        <v>-0.1586872064479966</v>
       </c>
       <c r="AC82" t="n">
-        <v>0.3523489932885908</v>
+        <v>0.4022810748115215</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
@@ -9848,7 +9842,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9909,28 +9903,28 @@
         <v>399.89</v>
       </c>
       <c r="V83" t="n">
-        <v>444.33</v>
+        <v>428.51</v>
       </c>
       <c r="W83" t="n">
         <v>10</v>
       </c>
       <c r="X83" t="n">
-        <v>44.43</v>
+        <v>42.85</v>
       </c>
       <c r="Y83" t="n">
         <v>0.1000157540566696</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>0.03560416807327882</v>
       </c>
       <c r="AA83" t="n">
         <v>0.005401485408487394</v>
       </c>
       <c r="AB83" t="n">
-        <v>-0.09515450228433819</v>
+        <v>-0.06174885066859581</v>
       </c>
       <c r="AC83" t="n">
-        <v>0.5082151699302275</v>
+        <v>0.5638273045507585</v>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
@@ -9964,7 +9958,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -10025,28 +10019,28 @@
         <v>389.9</v>
       </c>
       <c r="V84" t="n">
-        <v>433.23</v>
+        <v>417.8</v>
       </c>
       <c r="W84" t="n">
         <v>10</v>
       </c>
       <c r="X84" t="n">
-        <v>43.32</v>
+        <v>41.78</v>
       </c>
       <c r="Y84" t="n">
         <v>0.1000161576991437</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>0.03561618539805644</v>
       </c>
       <c r="AA84" t="n">
         <v>-0.1123364965375736</v>
       </c>
       <c r="AB84" t="n">
-        <v>-0.2011171894836461</v>
+        <v>-0.1716132120631881</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.3314866112650046</v>
+        <v>0.3805648635710865</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
@@ -10080,7 +10074,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -10141,28 +10135,28 @@
         <v>499.9</v>
       </c>
       <c r="V85" t="n">
-        <v>555.45</v>
+        <v>535.67</v>
       </c>
       <c r="W85" t="n">
         <v>10</v>
       </c>
       <c r="X85" t="n">
-        <v>55.54</v>
+        <v>53.56</v>
       </c>
       <c r="Y85" t="n">
         <v>0.1000090017103251</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>0.0356107660455488</v>
       </c>
       <c r="AA85" t="n">
         <v>-0.07333466693338664</v>
       </c>
       <c r="AB85" t="n">
-        <v>-0.1660095418129445</v>
+        <v>-0.1352138443444657</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.3901692473892688</v>
+        <v>0.4415608663181476</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
@@ -10196,7 +10190,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -10292,7 +10286,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -10353,28 +10347,28 @@
         <v>689.9</v>
       </c>
       <c r="V87" t="n">
-        <v>766.5599999999999</v>
+        <v>739.27</v>
       </c>
       <c r="W87" t="n">
         <v>10</v>
       </c>
       <c r="X87" t="n">
-        <v>76.65000000000001</v>
+        <v>73.92</v>
       </c>
       <c r="Y87" t="n">
         <v>0.1000052181173032</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>0.03560060530160714</v>
       </c>
       <c r="AA87" t="n">
         <v>-0.03075808088128718</v>
       </c>
       <c r="AB87" t="n">
-        <v>-0.1276873304111876</v>
+        <v>-0.09548608762698341</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.4540117416829745</v>
+        <v>0.5077110389610389</v>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
@@ -10408,7 +10402,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -10469,28 +10463,28 @@
         <v>454.9</v>
       </c>
       <c r="V88" t="n">
-        <v>516.9400000000001</v>
+        <v>498.53</v>
       </c>
       <c r="W88" t="n">
         <v>10</v>
       </c>
       <c r="X88" t="n">
-        <v>51.69</v>
+        <v>49.85</v>
       </c>
       <c r="Y88" t="n">
         <v>0.1200139281154488</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>0.03561341741788226</v>
       </c>
       <c r="AA88" t="n">
         <v>-0.07775335238513958</v>
       </c>
       <c r="AB88" t="n">
-        <v>-0.1884357952567031</v>
+        <v>-0.1584658897157644</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.3526794350938287</v>
+        <v>0.4026078234704111</v>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
@@ -10524,7 +10518,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -10585,28 +10579,28 @@
         <v>484.9</v>
       </c>
       <c r="V89" t="n">
-        <v>538.78</v>
+        <v>519.59</v>
       </c>
       <c r="W89" t="n">
         <v>10</v>
       </c>
       <c r="X89" t="n">
-        <v>53.87</v>
+        <v>51.95</v>
       </c>
       <c r="Y89" t="n">
         <v>0.100003712090278</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>0.03561750621775106</v>
       </c>
       <c r="AA89" t="n">
         <v>-0.06991132192204574</v>
       </c>
       <c r="AB89" t="n">
-        <v>-0.1629236423029807</v>
+        <v>-0.1320079293288939</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.3953963244848711</v>
+        <v>0.446968238691049</v>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
@@ -10640,7 +10634,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -10701,28 +10695,28 @@
         <v>479.9</v>
       </c>
       <c r="V90" t="n">
-        <v>533.23</v>
+        <v>514.24</v>
       </c>
       <c r="W90" t="n">
         <v>10</v>
       </c>
       <c r="X90" t="n">
-        <v>53.32</v>
+        <v>51.42</v>
       </c>
       <c r="Y90" t="n">
         <v>0.1000131275434616</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>0.03561315004782173</v>
       </c>
       <c r="AA90" t="n">
         <v>-0.05292769326943114</v>
       </c>
       <c r="AB90" t="n">
-        <v>-0.1476473566753559</v>
+        <v>-0.1161714374611077</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.4206676669167291</v>
+        <v>0.4731621936989499</v>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
@@ -10756,7 +10750,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -10817,28 +10811,28 @@
         <v>794.9</v>
       </c>
       <c r="V91" t="n">
-        <v>883.23</v>
+        <v>851.78</v>
       </c>
       <c r="W91" t="n">
         <v>10</v>
       </c>
       <c r="X91" t="n">
-        <v>88.31999999999999</v>
+        <v>85.17</v>
       </c>
       <c r="Y91" t="n">
         <v>0.1000079254554307</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>0.03560793904192572</v>
       </c>
       <c r="AA91" t="n">
         <v>-0.0708139388602339</v>
       </c>
       <c r="AB91" t="n">
-        <v>-0.1637399091969249</v>
+        <v>-0.132862945831083</v>
       </c>
       <c r="AC91" t="n">
-        <v>0.3937952898550725</v>
+        <v>0.4453446049078313</v>
       </c>
       <c r="AD91" t="inlineStr">
         <is>
@@ -10872,7 +10866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -10897,13 +10891,13 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Oportunidade: só a Roma tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -10926,19 +10920,39 @@
           <t>Pneu Goodyear Aro 14 Assurance Maxlife 175/70R14 88T XL</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
-      <c r="AB92" t="inlineStr"/>
-      <c r="AC92" t="inlineStr"/>
+      <c r="T92" t="n">
+        <v>461</v>
+      </c>
+      <c r="U92" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="V92" t="n">
+        <v>444.58</v>
+      </c>
+      <c r="W92" t="n">
+        <v>10</v>
+      </c>
+      <c r="X92" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0.03561822125813452</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>-0.07944082911544947</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>-0.1408970264069459</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.4321709786276713</v>
+      </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Concorrente sem estoque</t>
+          <t>Competitivo</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10982,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -11029,28 +11043,28 @@
         <v>639.9</v>
       </c>
       <c r="V93" t="n">
-        <v>711</v>
+        <v>685.6799999999999</v>
       </c>
       <c r="W93" t="n">
         <v>10</v>
       </c>
       <c r="X93" t="n">
-        <v>71.09999999999999</v>
+        <v>68.56</v>
       </c>
       <c r="Y93" t="n">
         <v>0.09999999999999998</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>0.03561181434599159</v>
       </c>
       <c r="AA93" t="n">
         <v>-0.06294733552117515</v>
       </c>
       <c r="AB93" t="n">
-        <v>-0.1566526019690576</v>
+        <v>-0.1255104421887761</v>
       </c>
       <c r="AC93" t="n">
-        <v>0.4056258790436007</v>
+        <v>0.4577012835472578</v>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
@@ -11084,7 +11098,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -11145,28 +11159,28 @@
         <v>329.9</v>
       </c>
       <c r="V94" t="n">
-        <v>374.89</v>
+        <v>361.54</v>
       </c>
       <c r="W94" t="n">
         <v>10</v>
       </c>
       <c r="X94" t="n">
-        <v>37.48</v>
+        <v>36.15</v>
       </c>
       <c r="Y94" t="n">
         <v>0.120008535837179</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>0.03561044573074756</v>
       </c>
       <c r="AA94" t="n">
         <v>-0.1257956956653531</v>
       </c>
       <c r="AB94" t="n">
-        <v>-0.2307076742511137</v>
+        <v>-0.2023012668031201</v>
       </c>
       <c r="AC94" t="n">
-        <v>0.2825506937033087</v>
+        <v>0.329737206085754</v>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
@@ -11200,7 +11214,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -11261,28 +11275,28 @@
         <v>509.9</v>
       </c>
       <c r="V95" t="n">
-        <v>579.4400000000001</v>
+        <v>558.8099999999999</v>
       </c>
       <c r="W95" t="n">
         <v>10</v>
       </c>
       <c r="X95" t="n">
-        <v>57.94</v>
+        <v>55.88</v>
       </c>
       <c r="Y95" t="n">
         <v>0.1200124257904185</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>0.03560334115697938</v>
       </c>
       <c r="AA95" t="n">
         <v>-0.02463228083938029</v>
       </c>
       <c r="AB95" t="n">
-        <v>-0.1416885268535139</v>
+        <v>-0.1100016105653083</v>
       </c>
       <c r="AC95" t="n">
-        <v>0.430617880566103</v>
+        <v>0.4833571939871153</v>
       </c>
       <c r="AD95" t="inlineStr">
         <is>
@@ -11316,7 +11330,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -11377,28 +11391,28 @@
         <v>434.9</v>
       </c>
       <c r="V96" t="n">
-        <v>511.65</v>
+        <v>493.43</v>
       </c>
       <c r="W96" t="n">
         <v>10</v>
       </c>
       <c r="X96" t="n">
-        <v>51.16</v>
+        <v>49.34</v>
       </c>
       <c r="Y96" t="n">
         <v>0.1500048861526434</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>0.03561028046516168</v>
       </c>
       <c r="AA96" t="n">
         <v>-0.06348585881811897</v>
       </c>
       <c r="AB96" t="n">
-        <v>-0.2039675559464477</v>
+        <v>-0.1745739010599274</v>
       </c>
       <c r="AC96" t="n">
-        <v>0.3268178264268959</v>
+        <v>0.3757600324280501</v>
       </c>
       <c r="AD96" t="inlineStr">
         <is>
@@ -11432,7 +11446,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -11493,28 +11507,28 @@
         <v>479.9</v>
       </c>
       <c r="V97" t="n">
-        <v>533.23</v>
+        <v>514.24</v>
       </c>
       <c r="W97" t="n">
         <v>10</v>
       </c>
       <c r="X97" t="n">
-        <v>53.32</v>
+        <v>51.42</v>
       </c>
       <c r="Y97" t="n">
         <v>0.1000131275434616</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>0.03561315004782173</v>
       </c>
       <c r="AA97" t="n">
         <v>-0.01650343821629496</v>
       </c>
       <c r="AB97" t="n">
-        <v>-0.1148660052885246</v>
+        <v>-0.08217952706907283</v>
       </c>
       <c r="AC97" t="n">
-        <v>0.4752438109527382</v>
+        <v>0.5297549591598598</v>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
@@ -11548,7 +11562,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -11609,28 +11623,28 @@
         <v>419.9</v>
       </c>
       <c r="V98" t="n">
-        <v>466.56</v>
+        <v>449.95</v>
       </c>
       <c r="W98" t="n">
         <v>10</v>
       </c>
       <c r="X98" t="n">
-        <v>46.65</v>
+        <v>44.99</v>
       </c>
       <c r="Y98" t="n">
         <v>0.1000085733882031</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>0.03560099451303156</v>
       </c>
       <c r="AA98" t="n">
         <v>-0.05084543939033093</v>
       </c>
       <c r="AB98" t="n">
-        <v>-0.1457690329218106</v>
+        <v>-0.1142349149905545</v>
       </c>
       <c r="AC98" t="n">
-        <v>0.4237942122186495</v>
+        <v>0.47632807290509</v>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
@@ -11664,7 +11678,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -11725,28 +11739,28 @@
         <v>749.89</v>
       </c>
       <c r="V99" t="n">
-        <v>833.22</v>
+        <v>803.55</v>
       </c>
       <c r="W99" t="n">
         <v>10</v>
       </c>
       <c r="X99" t="n">
-        <v>83.31999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="Y99" t="n">
         <v>0.1000096013057776</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>0.03560884280262122</v>
       </c>
       <c r="AA99" t="n">
         <v>-0.04184613743349019</v>
       </c>
       <c r="AB99" t="n">
-        <v>-0.1376707232183577</v>
+        <v>-0.1058303776989609</v>
       </c>
       <c r="AC99" t="n">
-        <v>0.4372299567930871</v>
+        <v>0.4903546981953952</v>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
@@ -11780,7 +11794,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -11876,7 +11890,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -11937,28 +11951,28 @@
         <v>474.9</v>
       </c>
       <c r="V101" t="n">
-        <v>527.67</v>
+        <v>508.88</v>
       </c>
       <c r="W101" t="n">
         <v>10</v>
       </c>
       <c r="X101" t="n">
-        <v>52.76</v>
+        <v>50.88</v>
       </c>
       <c r="Y101" t="n">
         <v>0.100005685371539</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>0.03560937707279166</v>
       </c>
       <c r="AA101" t="n">
         <v>-0.06136028637607915</v>
       </c>
       <c r="AB101" t="n">
-        <v>-0.1552295942539844</v>
+        <v>-0.1240371010847351</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.408074298711145</v>
+        <v>0.4601022012578617</v>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
@@ -11992,7 +12006,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -12053,28 +12067,28 @@
         <v>669.9</v>
       </c>
       <c r="V102" t="n">
-        <v>761.25</v>
+        <v>734.14</v>
       </c>
       <c r="W102" t="n">
         <v>10</v>
       </c>
       <c r="X102" t="n">
-        <v>76.12</v>
+        <v>73.41</v>
       </c>
       <c r="Y102" t="n">
         <v>0.12</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>0.03561247947454849</v>
       </c>
       <c r="AA102" t="n">
         <v>-0.005732198835647129</v>
       </c>
       <c r="AB102" t="n">
-        <v>-0.1250443349753695</v>
+        <v>-0.09273435584493428</v>
       </c>
       <c r="AC102" t="n">
-        <v>0.4583552285864425</v>
+        <v>0.5121917994823595</v>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
@@ -12108,7 +12122,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -12169,28 +12183,28 @@
         <v>419.9</v>
       </c>
       <c r="V103" t="n">
-        <v>466.56</v>
+        <v>449.95</v>
       </c>
       <c r="W103" t="n">
         <v>10</v>
       </c>
       <c r="X103" t="n">
-        <v>46.65</v>
+        <v>44.99</v>
       </c>
       <c r="Y103" t="n">
         <v>0.1000085733882031</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>0.03560099451303156</v>
       </c>
       <c r="AA103" t="n">
         <v>-0.02586330078590127</v>
       </c>
       <c r="AB103" t="n">
-        <v>-0.1232853223593964</v>
+        <v>-0.09092121346816306</v>
       </c>
       <c r="AC103" t="n">
-        <v>0.4613076098606645</v>
+        <v>0.5152256056901534</v>
       </c>
       <c r="AD103" t="inlineStr">
         <is>
@@ -12220,7 +12234,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -12281,28 +12295,28 @@
         <v>624.9</v>
       </c>
       <c r="V104" t="n">
-        <v>710.12</v>
+        <v>684.83</v>
       </c>
       <c r="W104" t="n">
         <v>10</v>
       </c>
       <c r="X104" t="n">
-        <v>71.01000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="Y104" t="n">
         <v>0.1200078859911001</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>0.03561369909311096</v>
       </c>
       <c r="AA104" t="n">
         <v>-0.01528244519123056</v>
       </c>
       <c r="AB104" t="n">
-        <v>-0.1334563172421562</v>
+        <v>-0.1014558357548588</v>
       </c>
       <c r="AC104" t="n">
-        <v>0.4443036192085621</v>
+        <v>0.497663551401869</v>
       </c>
       <c r="AD104" t="inlineStr">
         <is>
@@ -12336,7 +12350,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -12397,28 +12411,28 @@
         <v>919.9</v>
       </c>
       <c r="V105" t="n">
-        <v>1121.83</v>
+        <v>1081.89</v>
       </c>
       <c r="W105" t="n">
         <v>10</v>
       </c>
       <c r="X105" t="n">
-        <v>112.18</v>
+        <v>108.18</v>
       </c>
       <c r="Y105" t="n">
         <v>0.1800005348403947</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>0.03560254227467607</v>
       </c>
       <c r="AA105" t="n">
         <v>-0.006055005978910732</v>
       </c>
       <c r="AB105" t="n">
-        <v>-0.1849656365046396</v>
+        <v>-0.1548771132000482</v>
       </c>
       <c r="AC105" t="n">
-        <v>0.3584417899803884</v>
+        <v>0.4086707339619151</v>
       </c>
       <c r="AD105" t="inlineStr">
         <is>
@@ -12452,7 +12466,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -12513,28 +12527,28 @@
         <v>549.9</v>
       </c>
       <c r="V106" t="n">
-        <v>611</v>
+        <v>589.24</v>
       </c>
       <c r="W106" t="n">
         <v>10</v>
       </c>
       <c r="X106" t="n">
-        <v>61.1</v>
+        <v>58.92</v>
       </c>
       <c r="Y106" t="n">
         <v>0.1000000000000001</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>0.03561374795417349</v>
       </c>
       <c r="AA106" t="n">
         <v>-0.04629932715039087</v>
       </c>
       <c r="AB106" t="n">
-        <v>-0.1416693944353518</v>
+        <v>-0.1099721675378453</v>
       </c>
       <c r="AC106" t="n">
-        <v>0.4306055646481177</v>
+        <v>0.4835369993211134</v>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
@@ -12568,7 +12582,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -12629,28 +12643,28 @@
         <v>824.9</v>
       </c>
       <c r="V107" t="n">
-        <v>1005.98</v>
+        <v>970.16</v>
       </c>
       <c r="W107" t="n">
         <v>10</v>
       </c>
       <c r="X107" t="n">
-        <v>100.59</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="Y107" t="n">
         <v>0.1800035785999722</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>0.03560706972305616</v>
       </c>
       <c r="AA107" t="n">
         <v>-0.0410110316401987</v>
       </c>
       <c r="AB107" t="n">
-        <v>-0.2136324777828584</v>
+        <v>-0.184598416755999</v>
       </c>
       <c r="AC107" t="n">
-        <v>0.3106670643205089</v>
+        <v>0.3590351510153591</v>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
@@ -12684,7 +12698,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -12745,28 +12759,28 @@
         <v>589.9</v>
       </c>
       <c r="V108" t="n">
-        <v>670.35</v>
+        <v>646.48</v>
       </c>
       <c r="W108" t="n">
         <v>10</v>
       </c>
       <c r="X108" t="n">
-        <v>67.03</v>
+        <v>64.64</v>
       </c>
       <c r="Y108" t="n">
         <v>0.1200119340642949</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>0.03560826433952413</v>
       </c>
       <c r="AA108" t="n">
         <v>-0.01464655026275641</v>
       </c>
       <c r="AB108" t="n">
-        <v>-0.1329007235026479</v>
+        <v>-0.1008847914862022</v>
       </c>
       <c r="AC108" t="n">
-        <v>0.4453229897061017</v>
+        <v>0.4987623762376237</v>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
@@ -12800,7 +12814,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -12861,28 +12875,28 @@
         <v>519.9</v>
       </c>
       <c r="V109" t="n">
-        <v>590.8</v>
+        <v>569.76</v>
       </c>
       <c r="W109" t="n">
         <v>10</v>
       </c>
       <c r="X109" t="n">
-        <v>59.08</v>
+        <v>56.97</v>
       </c>
       <c r="Y109" t="n">
         <v>0.1200067704807041</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>0.03561272850372366</v>
       </c>
       <c r="AA109" t="n">
         <v>0.3804770148105405</v>
       </c>
       <c r="AB109" t="n">
-        <v>0.2148104265402846</v>
+        <v>0.2596707385565853</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.024712254570074</v>
+        <v>1.099701597331929</v>
       </c>
       <c r="AD109" t="inlineStr">
         <is>
@@ -12916,7 +12930,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -12977,28 +12991,28 @@
         <v>539.9</v>
       </c>
       <c r="V110" t="n">
-        <v>599.89</v>
+        <v>578.53</v>
       </c>
       <c r="W110" t="n">
         <v>10</v>
       </c>
       <c r="X110" t="n">
-        <v>59.98</v>
+        <v>57.85</v>
       </c>
       <c r="Y110" t="n">
         <v>0.1000016669722783</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>0.03560652786344165</v>
       </c>
       <c r="AA110" t="n">
         <v>-0.04321170587145751</v>
       </c>
       <c r="AB110" t="n">
-        <v>-0.1388921302238743</v>
+        <v>-0.1070990268438974</v>
       </c>
       <c r="AC110" t="n">
-        <v>0.4354784928309436</v>
+        <v>0.4883318928262748</v>
       </c>
       <c r="AD110" t="inlineStr">
         <is>
@@ -13028,7 +13042,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -13089,28 +13103,28 @@
         <v>1199.9</v>
       </c>
       <c r="V111" t="n">
-        <v>1363.53</v>
+        <v>1314.98</v>
       </c>
       <c r="W111" t="n">
         <v>10</v>
       </c>
       <c r="X111" t="n">
-        <v>136.35</v>
+        <v>131.49</v>
       </c>
       <c r="Y111" t="n">
         <v>0.1200046936994418</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>0.03560611060996088</v>
       </c>
       <c r="AA111" t="n">
         <v>-0.06241353446120523</v>
       </c>
       <c r="AB111" t="n">
-        <v>-0.1749283110749305</v>
+        <v>-0.1444660755296658</v>
       </c>
       <c r="AC111" t="n">
-        <v>0.3751375137513753</v>
+        <v>0.4259639516313027</v>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
@@ -13144,7 +13158,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -13167,11 +13181,15 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Oportunidade: só a Roma tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -13189,20 +13207,44 @@
       <c r="R112" t="n">
         <v>85.95</v>
       </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Pneu Goodyear Aro 15 EfficientGrip Performance 195/65R15 91H</t>
+        </is>
+      </c>
+      <c r="T112" t="n">
+        <v>588.78</v>
+      </c>
+      <c r="U112" t="n">
+        <v>529.9</v>
+      </c>
+      <c r="V112" t="n">
+        <v>567.8099999999999</v>
+      </c>
+      <c r="W112" t="n">
+        <v>10</v>
+      </c>
+      <c r="X112" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0.1000033968545128</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0.03561601956588201</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>-0.02681638044914125</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>-0.09179126820591377</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0.5137372314195139</v>
+      </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Sem dado</t>
+          <t>Na média</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13274,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -13293,28 +13335,28 @@
         <v>749.9</v>
       </c>
       <c r="V113" t="n">
-        <v>833.23</v>
+        <v>803.5599999999999</v>
       </c>
       <c r="W113" t="n">
         <v>10</v>
       </c>
       <c r="X113" t="n">
-        <v>83.31999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="Y113" t="n">
         <v>0.1000084010417293</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>0.03560841544351512</v>
       </c>
       <c r="AA113" t="n">
         <v>-0.02671022803040402</v>
       </c>
       <c r="AB113" t="n">
-        <v>-0.1240473818753526</v>
+        <v>-0.09170441535168494</v>
       </c>
       <c r="AC113" t="n">
-        <v>0.459913586173788</v>
+        <v>0.5138767890479154</v>
       </c>
       <c r="AD113" t="inlineStr">
         <is>
@@ -13348,7 +13390,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -13409,28 +13451,28 @@
         <v>479.9</v>
       </c>
       <c r="V114" t="n">
-        <v>545.35</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="W114" t="n">
         <v>10</v>
       </c>
       <c r="X114" t="n">
-        <v>54.53</v>
+        <v>52.59</v>
       </c>
       <c r="Y114" t="n">
         <v>0.1200146694783167</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>0.0356101586137344</v>
       </c>
       <c r="AA114" t="n">
         <v>-0.03588247551573243</v>
       </c>
       <c r="AB114" t="n">
-        <v>-0.1515907215549647</v>
+        <v>-0.120263152891069</v>
       </c>
       <c r="AC114" t="n">
-        <v>0.4140839904639648</v>
+        <v>0.4662483361855865</v>
       </c>
       <c r="AD114" t="inlineStr">
         <is>
@@ -13464,7 +13506,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13560,7 +13602,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13621,28 +13663,28 @@
         <v>409.9</v>
       </c>
       <c r="V116" t="n">
-        <v>455.45</v>
+        <v>439.23</v>
       </c>
       <c r="W116" t="n">
         <v>10</v>
       </c>
       <c r="X116" t="n">
-        <v>45.54</v>
+        <v>43.92</v>
       </c>
       <c r="Y116" t="n">
         <v>0.1000109781534746</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>0.03561312987155552</v>
       </c>
       <c r="AA116" t="n">
         <v>0.06189314466943152</v>
       </c>
       <c r="AB116" t="n">
-        <v>-0.04430782742342743</v>
+        <v>-0.009015777610819065</v>
       </c>
       <c r="AC116" t="n">
-        <v>0.5928853754940713</v>
+        <v>0.6516393442622952</v>
       </c>
       <c r="AD116" t="inlineStr">
         <is>
@@ -13676,7 +13718,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13737,28 +13779,28 @@
         <v>549.9</v>
       </c>
       <c r="V117" t="n">
-        <v>611</v>
+        <v>589.24</v>
       </c>
       <c r="W117" t="n">
         <v>10</v>
       </c>
       <c r="X117" t="n">
-        <v>61.1</v>
+        <v>58.92</v>
       </c>
       <c r="Y117" t="n">
         <v>0.1000000000000001</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>0.03561374795417349</v>
       </c>
       <c r="AA117" t="n">
         <v>0.007746863066012022</v>
       </c>
       <c r="AB117" t="n">
-        <v>-0.09302782324058922</v>
+        <v>-0.05953431538931508</v>
       </c>
       <c r="AC117" t="n">
-        <v>0.511620294599018</v>
+        <v>0.5675492192803802</v>
       </c>
       <c r="AD117" t="inlineStr">
         <is>
@@ -13792,7 +13834,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -13853,28 +13895,28 @@
         <v>789.9</v>
       </c>
       <c r="V118" t="n">
-        <v>877.67</v>
+        <v>846.42</v>
       </c>
       <c r="W118" t="n">
         <v>10</v>
       </c>
       <c r="X118" t="n">
-        <v>87.76000000000001</v>
+        <v>84.64</v>
       </c>
       <c r="Y118" t="n">
         <v>0.1000034181412148</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>0.03560563765424363</v>
       </c>
       <c r="AA118" t="n">
         <v>-0.0250791239397391</v>
       </c>
       <c r="AB118" t="n">
-        <v>-0.1225745439629928</v>
+        <v>-0.09017981616691473</v>
       </c>
       <c r="AC118" t="n">
-        <v>0.4625113947128532</v>
+        <v>0.5164224952741021</v>
       </c>
       <c r="AD118" t="inlineStr">
         <is>
@@ -13908,7 +13950,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -13969,28 +14011,28 @@
         <v>689.9</v>
       </c>
       <c r="V119" t="n">
-        <v>766.5599999999999</v>
+        <v>739.27</v>
       </c>
       <c r="W119" t="n">
         <v>10</v>
       </c>
       <c r="X119" t="n">
-        <v>76.65000000000001</v>
+        <v>73.92</v>
       </c>
       <c r="Y119" t="n">
         <v>0.1000052181173032</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>0.03560060530160714</v>
       </c>
       <c r="AA119" t="n">
         <v>-0.072575735613857</v>
       </c>
       <c r="AB119" t="n">
-        <v>-0.1653230014610727</v>
+        <v>-0.1345110717329256</v>
       </c>
       <c r="AC119" t="n">
-        <v>0.391258969341161</v>
+        <v>0.4426406926406927</v>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
@@ -14024,7 +14066,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -14085,28 +14127,28 @@
         <v>399.89</v>
       </c>
       <c r="V120" t="n">
-        <v>444.33</v>
+        <v>428.51</v>
       </c>
       <c r="W120" t="n">
         <v>10</v>
       </c>
       <c r="X120" t="n">
-        <v>44.43</v>
+        <v>42.85</v>
       </c>
       <c r="Y120" t="n">
         <v>0.1000157540566696</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>0.03560416807327882</v>
       </c>
       <c r="AA120" t="n">
         <v>0.005401485408487394</v>
       </c>
       <c r="AB120" t="n">
-        <v>-0.09515450228433819</v>
+        <v>-0.06174885066859581</v>
       </c>
       <c r="AC120" t="n">
-        <v>0.5082151699302275</v>
+        <v>0.5638273045507585</v>
       </c>
       <c r="AD120" t="inlineStr">
         <is>
@@ -14140,7 +14182,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -14201,28 +14243,28 @@
         <v>759.89</v>
       </c>
       <c r="V121" t="n">
-        <v>844.33</v>
+        <v>814.27</v>
       </c>
       <c r="W121" t="n">
         <v>10</v>
       </c>
       <c r="X121" t="n">
-        <v>84.43000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="Y121" t="n">
         <v>0.1000082905972783</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>0.03560219345516569</v>
       </c>
       <c r="AA121" t="n">
         <v>-0.002684599086709816</v>
       </c>
       <c r="AB121" t="n">
-        <v>-0.1024244075183873</v>
+        <v>-0.06928905645547545</v>
       </c>
       <c r="AC121" t="n">
-        <v>0.4960322160369537</v>
+        <v>0.5513387374109555</v>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
@@ -14256,7 +14298,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -14317,28 +14359,28 @@
         <v>599.9</v>
       </c>
       <c r="V122" t="n">
-        <v>731.59</v>
+        <v>705.54</v>
       </c>
       <c r="W122" t="n">
         <v>10</v>
       </c>
       <c r="X122" t="n">
-        <v>73.15000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="Y122" t="n">
         <v>0.1800051941661314</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>0.03560737571590655</v>
       </c>
       <c r="AA122" t="n">
         <v>-0.03253875645940985</v>
       </c>
       <c r="AB122" t="n">
-        <v>-0.2066868054511407</v>
+        <v>-0.1773960370779828</v>
       </c>
       <c r="AC122" t="n">
-        <v>0.3223513328776486</v>
+        <v>0.3710843373493977</v>
       </c>
       <c r="AD122" t="inlineStr">
         <is>
@@ -14368,7 +14410,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -14429,28 +14471,28 @@
         <v>469.9</v>
       </c>
       <c r="V123" t="n">
-        <v>522.12</v>
+        <v>503.53</v>
       </c>
       <c r="W123" t="n">
         <v>10</v>
       </c>
       <c r="X123" t="n">
-        <v>52.21</v>
+        <v>50.35</v>
       </c>
       <c r="Y123" t="n">
         <v>0.1000153221481652</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>0.03560484179882029</v>
       </c>
       <c r="AA123" t="n">
         <v>-0.05137263247499468</v>
       </c>
       <c r="AB123" t="n">
-        <v>-0.146249904236574</v>
+        <v>-0.1147300061565348</v>
       </c>
       <c r="AC123" t="n">
-        <v>0.4229074889867843</v>
+        <v>0.4754716981132077</v>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
@@ -14480,7 +14522,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14572,7 +14614,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -14633,28 +14675,28 @@
         <v>1199.9</v>
       </c>
       <c r="V125" t="n">
-        <v>1333.23</v>
+        <v>1285.76</v>
       </c>
       <c r="W125" t="n">
         <v>10</v>
       </c>
       <c r="X125" t="n">
-        <v>133.32</v>
+        <v>128.57</v>
       </c>
       <c r="Y125" t="n">
         <v>0.1000052504069064</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>0.03560525940760406</v>
       </c>
       <c r="AA125" t="n">
         <v>-0.03250270855904658</v>
       </c>
       <c r="AB125" t="n">
-        <v>-0.1292575174576029</v>
+        <v>-0.09710988053758085</v>
       </c>
       <c r="AC125" t="n">
-        <v>0.4512451245124511</v>
+        <v>0.5048611651240569</v>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
@@ -14688,7 +14730,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14749,28 +14791,28 @@
         <v>489.9</v>
       </c>
       <c r="V126" t="n">
-        <v>556.71</v>
+        <v>536.89</v>
       </c>
       <c r="W126" t="n">
         <v>10</v>
       </c>
       <c r="X126" t="n">
-        <v>55.67</v>
+        <v>53.68</v>
       </c>
       <c r="Y126" t="n">
         <v>0.120008622083311</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>0.03560201900450877</v>
       </c>
       <c r="AA126" t="n">
         <v>-0.07225964482547453</v>
       </c>
       <c r="AB126" t="n">
-        <v>-0.1835964865010509</v>
+        <v>-0.1534578777775708</v>
       </c>
       <c r="AC126" t="n">
-        <v>0.3606969642536375</v>
+        <v>0.411140089418778</v>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
@@ -14804,7 +14846,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14865,28 +14907,28 @@
         <v>634.9</v>
       </c>
       <c r="V127" t="n">
-        <v>705.45</v>
+        <v>680.33</v>
       </c>
       <c r="W127" t="n">
         <v>10</v>
       </c>
       <c r="X127" t="n">
-        <v>70.54000000000001</v>
+        <v>68.03</v>
       </c>
       <c r="Y127" t="n">
         <v>0.100007087674534</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>0.03560847685874269</v>
       </c>
       <c r="AA127" t="n">
         <v>-0.07760277209009292</v>
       </c>
       <c r="AB127" t="n">
-        <v>-0.1698490325324262</v>
+        <v>-0.1391971543221673</v>
       </c>
       <c r="AC127" t="n">
-        <v>0.3836121349588884</v>
+        <v>0.4346611788916654</v>
       </c>
       <c r="AD127" t="inlineStr">
         <is>
@@ -14920,7 +14962,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -15016,7 +15058,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -15077,28 +15119,28 @@
         <v>589.9</v>
       </c>
       <c r="V129" t="n">
-        <v>670.35</v>
+        <v>646.48</v>
       </c>
       <c r="W129" t="n">
         <v>10</v>
       </c>
       <c r="X129" t="n">
-        <v>67.03</v>
+        <v>64.64</v>
       </c>
       <c r="Y129" t="n">
         <v>0.1200119340642949</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>0.03560826433952413</v>
       </c>
       <c r="AA129" t="n">
         <v>0.0001695202576708077</v>
       </c>
       <c r="AB129" t="n">
-        <v>-0.1198627582606102</v>
+        <v>-0.08736542507115463</v>
       </c>
       <c r="AC129" t="n">
-        <v>0.4669550947337013</v>
+        <v>0.521194306930693</v>
       </c>
       <c r="AD129" t="inlineStr">
         <is>
@@ -15128,7 +15170,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -15189,19 +15231,19 @@
         <v>569.9</v>
       </c>
       <c r="V130" t="n">
-        <v>633.23</v>
+        <v>610.6799999999999</v>
       </c>
       <c r="W130" t="n">
         <v>10</v>
       </c>
       <c r="X130" t="n">
-        <v>63.32</v>
+        <v>61.06</v>
       </c>
       <c r="Y130" t="n">
         <v>0.1000110544351974</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>0.03561107338565772</v>
       </c>
       <c r="AA130" t="n">
         <v>-1</v>
@@ -15244,7 +15286,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15305,28 +15347,28 @@
         <v>769.9</v>
       </c>
       <c r="V131" t="n">
-        <v>938.91</v>
+        <v>905.48</v>
       </c>
       <c r="W131" t="n">
         <v>10</v>
       </c>
       <c r="X131" t="n">
-        <v>93.89</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="Y131" t="n">
         <v>0.180006603401817</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>0.03560511657134335</v>
       </c>
       <c r="AA131" t="n">
         <v>-0.05766982725029224</v>
       </c>
       <c r="AB131" t="n">
-        <v>-0.2272954809300146</v>
+        <v>-0.1987675045279852</v>
       </c>
       <c r="AC131" t="n">
-        <v>0.2878900841410161</v>
+        <v>0.3355423017450849</v>
       </c>
       <c r="AD131" t="inlineStr">
         <is>
@@ -15356,7 +15398,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15448,7 +15490,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15540,7 +15582,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15601,28 +15643,28 @@
         <v>1079.9</v>
       </c>
       <c r="V134" t="n">
-        <v>1199.89</v>
+        <v>1157.17</v>
       </c>
       <c r="W134" t="n">
         <v>10</v>
       </c>
       <c r="X134" t="n">
-        <v>119.98</v>
+        <v>115.71</v>
       </c>
       <c r="Y134" t="n">
         <v>0.1000008334097292</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>0.03560326363249966</v>
       </c>
       <c r="AA134" t="n">
         <v>-0.01489026761737211</v>
       </c>
       <c r="AB134" t="n">
-        <v>-0.1134020618556703</v>
+        <v>-0.08067094722469481</v>
       </c>
       <c r="AC134" t="n">
-        <v>0.4777462910485082</v>
+        <v>0.5322789732953075</v>
       </c>
       <c r="AD134" t="inlineStr">
         <is>
@@ -15652,7 +15694,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15744,7 +15786,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15769,13 +15811,13 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N136" t="n">
@@ -15798,39 +15840,19 @@
           <t>Pneu Goodyear Aro 15 Cargo Marathon 2 195/70R15C 104/102R 10 Lonas</t>
         </is>
       </c>
-      <c r="T136" t="n">
-        <v>931.7</v>
-      </c>
-      <c r="U136" t="n">
-        <v>819.89</v>
-      </c>
-      <c r="V136" t="n">
-        <v>931.7</v>
-      </c>
-      <c r="W136" t="n">
-        <v>10</v>
-      </c>
-      <c r="X136" t="n">
-        <v>93.17</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0.1200064398411507</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>-0.02556440498115609</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>-0.1425029515938607</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0.4292154126864871</v>
-      </c>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15882,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -15921,28 +15943,28 @@
         <v>1049.9</v>
       </c>
       <c r="V137" t="n">
-        <v>1166.56</v>
+        <v>1125.03</v>
       </c>
       <c r="W137" t="n">
         <v>10</v>
       </c>
       <c r="X137" t="n">
-        <v>116.65</v>
+        <v>112.5</v>
       </c>
       <c r="Y137" t="n">
         <v>0.1000034288849265</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>0.03560039775065149</v>
       </c>
       <c r="AA137" t="n">
         <v>-0.05669111343937527</v>
       </c>
       <c r="AB137" t="n">
-        <v>-0.1510252365930599</v>
+        <v>-0.119685697270295</v>
       </c>
       <c r="AC137" t="n">
-        <v>0.4150021431633091</v>
+        <v>0.4672000000000001</v>
       </c>
       <c r="AD137" t="inlineStr">
         <is>
@@ -15972,7 +15994,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -16064,7 +16086,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -16160,7 +16182,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -16221,28 +16243,28 @@
         <v>689.9</v>
       </c>
       <c r="V140" t="n">
-        <v>811.65</v>
+        <v>782.75</v>
       </c>
       <c r="W140" t="n">
         <v>10</v>
       </c>
       <c r="X140" t="n">
-        <v>81.16</v>
+        <v>78.27</v>
       </c>
       <c r="Y140" t="n">
         <v>0.1500030801453829</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>0.03560648062588556</v>
       </c>
       <c r="AA140" t="n">
         <v>-0.07511233512103199</v>
       </c>
       <c r="AB140" t="n">
-        <v>-0.2138483336413478</v>
+        <v>-0.18482274033855</v>
       </c>
       <c r="AC140" t="n">
-        <v>0.3103745687530803</v>
+        <v>0.358758144883097</v>
       </c>
       <c r="AD140" t="inlineStr">
         <is>
@@ -16272,7 +16294,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -16364,7 +16386,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -16448,7 +16470,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50</t>
+          <t>2026-10-26 11:26</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -16509,28 +16531,28 @@
         <v>1349.9</v>
       </c>
       <c r="V143" t="n">
-        <v>1499.89</v>
+        <v>1446.49</v>
       </c>
       <c r="W143" t="n">
         <v>10</v>
       </c>
       <c r="X143" t="n">
-        <v>149.98</v>
+        <v>144.64</v>
       </c>
       <c r="Y143" t="n">
         <v>0.1000006667155592</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>0.03560261085812966</v>
       </c>
       <c r="AA143" t="n">
         <v>-0.08693977331654201</v>
       </c>
       <c r="AB143" t="n">
-        <v>-0.1782464047363475</v>
+        <v>-0.1479097677827016</v>
       </c>
       <c r="AC143" t="n">
-        <v>0.3696492865715428</v>
+        <v>0.4202157079646018</v>
       </c>
       <c r="AD143" t="inlineStr">
         <is>
